--- a/communication/protocol/EtherCAT_LAN925x/ecat_app.xlsx
+++ b/communication/protocol/EtherCAT_LAN925x/ecat_app.xlsx
@@ -527,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T141"/>
+  <dimension ref="A1:T151"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.7265625" defaultRowHeight="14" outlineLevelRow="1"/>
   <cols>
     <col width="3.90625" customWidth="1" style="20" min="1" max="1"/>
@@ -3656,22 +3656,17 @@
     <row r="113">
       <c r="B113" t="inlineStr">
         <is>
-          <t>0x606B</t>
+          <t>0x60C2</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>VARIABLE</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>DINT</t>
+          <t>RECORD</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Velocity_demand_value</t>
+          <t>Interpolation_time_period</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -3679,73 +3674,55 @@
           <t>ro</t>
         </is>
       </c>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>tx</t>
-        </is>
-      </c>
+      <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr">
         <is>
-          <t>EtherCAT_Read_0x606B_Callback</t>
+          <t>EtherCAT_Read_0x60C2_Callback</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>EtherCAT_Write_0x60C2_Callback</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>0x606C</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>VARIABLE</t>
-        </is>
+      <c r="D114" t="n">
+        <v>1</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>DINT</t>
+          <t>USINT</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Velocity_actual_value</t>
+          <t>Interpolation_time_period_Ip_time_units</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>ro</t>
+          <t>rw</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>tx</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr">
-        <is>
-          <t>EtherCAT_Read_0x606C_Callback</t>
+          <t>rx</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>0x606D</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>VARIABLE</t>
-        </is>
+      <c r="D115" t="n">
+        <v>2</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>UINT</t>
+          <t>SINT</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Velocity_window</t>
+          <t>Interpolation_time_period_Ip_time_index</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -3756,23 +3733,13 @@
       <c r="M115" t="inlineStr">
         <is>
           <t>rx</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr">
-        <is>
-          <t>EtherCAT_Read_0x606D_Callback</t>
-        </is>
-      </c>
-      <c r="O115" t="inlineStr">
-        <is>
-          <t>EtherCAT_Write_0x606D_Callback</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="B116" t="inlineStr">
         <is>
-          <t>0x606E</t>
+          <t>0x606B</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3782,39 +3749,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>UINT</t>
+          <t>DINT</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Velocity_window_time</t>
+          <t>Velocity_demand_value</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>rw</t>
+          <t>ro</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>rx</t>
+          <t>tx</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>EtherCAT_Read_0x606E_Callback</t>
-        </is>
-      </c>
-      <c r="O116" t="inlineStr">
-        <is>
-          <t>EtherCAT_Write_0x606E_Callback</t>
+          <t>EtherCAT_Read_0x606B_Callback</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="B117" t="inlineStr">
         <is>
-          <t>0x606F</t>
+          <t>0x606C</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3824,39 +3786,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>UINT</t>
+          <t>DINT</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Velocity_threshold</t>
+          <t>Velocity_actual_value</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>rw</t>
+          <t>ro</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>rx</t>
+          <t>tx</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>EtherCAT_Read_0x606F_Callback</t>
-        </is>
-      </c>
-      <c r="O117" t="inlineStr">
-        <is>
-          <t>EtherCAT_Write_0x606F_Callback</t>
+          <t>EtherCAT_Read_0x606C_Callback</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="B118" t="inlineStr">
         <is>
-          <t>0x6070</t>
+          <t>0x606D</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3871,7 +3828,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Velocity_threshold_time</t>
+          <t>Velocity_window</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -3886,19 +3843,19 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>EtherCAT_Read_0x6070_Callback</t>
+          <t>EtherCAT_Read_0x606D_Callback</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>EtherCAT_Write_0x6070_Callback</t>
+          <t>EtherCAT_Write_0x606D_Callback</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="B119" t="inlineStr">
         <is>
-          <t>0x60FF</t>
+          <t>0x606E</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3908,12 +3865,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>DINT</t>
+          <t>UINT</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Target_velocity</t>
+          <t>Velocity_window_time</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -3928,19 +3885,19 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>EtherCAT_Read_0x60FF_Callback</t>
+          <t>EtherCAT_Read_0x606E_Callback</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>EtherCAT_Write_0x60FF_Callback</t>
+          <t>EtherCAT_Write_0x606E_Callback</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="B120" t="inlineStr">
         <is>
-          <t>0x6071</t>
+          <t>0x606F</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3950,12 +3907,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>UINT</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Target_torque</t>
+          <t>Velocity_threshold</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -3970,19 +3927,19 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>EtherCAT_Read_0x6071_Callback</t>
+          <t>EtherCAT_Read_0x606F_Callback</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>EtherCAT_Write_0x6071_Callback</t>
+          <t>EtherCAT_Write_0x606F_Callback</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="B121" t="inlineStr">
         <is>
-          <t>0x6072</t>
+          <t>0x6070</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3997,7 +3954,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Max_torque</t>
+          <t>Velocity_threshold_time</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -4012,19 +3969,19 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>EtherCAT_Read_0x6072_Callback</t>
+          <t>EtherCAT_Read_0x6070_Callback</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>EtherCAT_Write_0x6072_Callback</t>
+          <t>EtherCAT_Write_0x6070_Callback</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="B122" t="inlineStr">
         <is>
-          <t>0x6073</t>
+          <t>0x60FF</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4034,12 +3991,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>UINT</t>
+          <t>DINT</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Max_current</t>
+          <t>Target_velocity</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -4054,19 +4011,19 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>EtherCAT_Read_0x6073_Callback</t>
+          <t>EtherCAT_Read_0x60FF_Callback</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>EtherCAT_Write_0x6073_Callback</t>
+          <t>EtherCAT_Write_0x60FF_Callback</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="B123" t="inlineStr">
         <is>
-          <t>0x6074</t>
+          <t>0x6071</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4081,29 +4038,34 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Torque_demand_value</t>
+          <t>Target_torque</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>ro</t>
+          <t>rw</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>tx</t>
+          <t>rx</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>EtherCAT_Read_0x6074_Callback</t>
+          <t>EtherCAT_Read_0x6071_Callback</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>EtherCAT_Write_0x6071_Callback</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="B124" t="inlineStr">
         <is>
-          <t>0x6075</t>
+          <t>0x6072</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4113,12 +4075,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>UDINT</t>
+          <t>UINT</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Motor_rated_current</t>
+          <t>Max_torque</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -4133,19 +4095,19 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>EtherCAT_Read_0x6075_Callback</t>
+          <t>EtherCAT_Read_0x6072_Callback</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>EtherCAT_Write_0x6075_Callback</t>
+          <t>EtherCAT_Write_0x6072_Callback</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="B125" t="inlineStr">
         <is>
-          <t>0x6076</t>
+          <t>0x6073</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4155,12 +4117,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>UDINT</t>
+          <t>UINT</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Motor_rated_torque</t>
+          <t>Max_current</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -4175,19 +4137,19 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>EtherCAT_Read_0x6076_Callback</t>
+          <t>EtherCAT_Read_0x6073_Callback</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>EtherCAT_Write_0x6076_Callback</t>
+          <t>EtherCAT_Write_0x6073_Callback</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="B126" t="inlineStr">
         <is>
-          <t>0x6077</t>
+          <t>0x6074</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4202,7 +4164,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Torque_actual_value</t>
+          <t>Torque_demand_value</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -4217,14 +4179,14 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>EtherCAT_Read_0x6077_Callback</t>
+          <t>EtherCAT_Read_0x6074_Callback</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="B127" t="inlineStr">
         <is>
-          <t>0x6078</t>
+          <t>0x6075</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4234,34 +4196,39 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>UDINT</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Current_actual_value</t>
+          <t>Motor_rated_current</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>ro</t>
+          <t>rw</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>tx</t>
+          <t>rx</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>EtherCAT_Read_0x6078_Callback</t>
+          <t>EtherCAT_Read_0x6075_Callback</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>EtherCAT_Write_0x6075_Callback</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="B128" t="inlineStr">
         <is>
-          <t>0x6079</t>
+          <t>0x6076</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4276,325 +4243,687 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>DC_link_circuit_voltage</t>
+          <t>Motor_rated_torque</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>ro</t>
+          <t>rw</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>tx</t>
+          <t>rx</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>EtherCAT_Read_0x6079_Callback</t>
+          <t>EtherCAT_Read_0x6076_Callback</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>EtherCAT_Write_0x6076_Callback</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="B129" t="inlineStr">
         <is>
+          <t>0x6077</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>VARIABLE</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Torque_actual_value</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>tx</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>EtherCAT_Read_0x6077_Callback</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>0x6078</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>VARIABLE</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Current_actual_value</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>tx</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>EtherCAT_Read_0x6078_Callback</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>0x6079</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>VARIABLE</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>UDINT</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>DC_link_circuit_voltage</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>tx</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>EtherCAT_Read_0x6079_Callback</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" t="inlineStr">
+        <is>
           <t>0x6087</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
+      <c r="C132" t="inlineStr">
         <is>
           <t>VARIABLE</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
+      <c r="E132" t="inlineStr">
         <is>
           <t>UDINT</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr">
+      <c r="F132" t="inlineStr">
         <is>
           <t>Torque_slope</t>
         </is>
       </c>
-      <c r="L129" t="inlineStr">
-        <is>
-          <t>rw</t>
-        </is>
-      </c>
-      <c r="M129" t="inlineStr">
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>rw</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
         <is>
           <t>rx</t>
         </is>
       </c>
-      <c r="N129" t="inlineStr">
+      <c r="N132" t="inlineStr">
         <is>
           <t>EtherCAT_Read_0x6087_Callback</t>
         </is>
       </c>
-      <c r="O129" t="inlineStr">
+      <c r="O132" t="inlineStr">
         <is>
           <t>EtherCAT_Write_0x6087_Callback</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="B130" s="9" t="inlineStr">
+    <row r="133">
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>0x60B0</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>VARIABLE</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>DINT</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Position_offset</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>rw</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>rx</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>EtherCAT_Read_0x60B0_Callback</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>EtherCAT_Write_0x60B0_Callback</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>0x60B1</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>VARIABLE</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>DINT</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Velocity_offset</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>rw</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>rx</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>EtherCAT_Read_0x60B1_Callback</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>EtherCAT_Write_0x60B1_Callback</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>0x60B2</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>VARIABLE</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Torque_offset</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>rw</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>rx</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>EtherCAT_Read_0x60B2_Callback</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>EtherCAT_Write_0x60B2_Callback</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>0x60FD</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>VARIABLE</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>UDINT</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Digital_inputs</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>tx</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>EtherCAT_Read_0x60FD_Callback</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>0x60FE</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>RECORD</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Digital_outputs</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>EtherCAT_Read_0x60FE_Callback</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>EtherCAT_Write_0x60FE_Callback</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="D138" t="n">
+        <v>1</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>UDINT</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Digital_outputs_Physical_outputs</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>rw</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>rx</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="D139" t="n">
+        <v>2</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>UDINT</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Digital_outputs_Bit_mask</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>rw</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>rx</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" s="9" t="inlineStr">
         <is>
           <t>//0x7nnx</t>
         </is>
       </c>
-      <c r="C130" s="9" t="inlineStr">
+      <c r="C140" s="9" t="inlineStr">
         <is>
           <t>Output Data of the Module (0x7000 - 0x7FFF)</t>
         </is>
       </c>
-      <c r="D130" s="9" t="n"/>
-      <c r="E130" s="9" t="n"/>
-      <c r="F130" s="9" t="n"/>
-      <c r="G130" s="9" t="n"/>
-      <c r="H130" s="9" t="n"/>
-      <c r="I130" s="9" t="n"/>
-      <c r="J130" s="9" t="n"/>
-      <c r="K130" s="9" t="n"/>
-      <c r="L130" s="9" t="n"/>
-      <c r="M130" s="9" t="n"/>
-      <c r="N130" s="9" t="n"/>
-      <c r="O130" s="9" t="n"/>
-      <c r="P130" s="9" t="n"/>
-    </row>
-    <row r="131">
-      <c r="B131" s="15" t="inlineStr">
+      <c r="D140" s="9" t="n"/>
+      <c r="E140" s="9" t="n"/>
+      <c r="F140" s="9" t="n"/>
+      <c r="G140" s="9" t="n"/>
+      <c r="H140" s="9" t="n"/>
+      <c r="I140" s="9" t="n"/>
+      <c r="J140" s="9" t="n"/>
+      <c r="K140" s="9" t="n"/>
+      <c r="L140" s="9" t="n"/>
+      <c r="M140" s="9" t="n"/>
+      <c r="N140" s="9" t="n"/>
+      <c r="O140" s="9" t="n"/>
+      <c r="P140" s="9" t="n"/>
+    </row>
+    <row r="141">
+      <c r="B141" s="15" t="inlineStr">
         <is>
           <t>0x7010</t>
         </is>
       </c>
-      <c r="C131" s="15" t="inlineStr">
+      <c r="C141" s="15" t="inlineStr">
         <is>
           <t>VARIABLE</t>
         </is>
       </c>
-      <c r="D131" s="12" t="n"/>
-      <c r="E131" s="14" t="inlineStr">
+      <c r="D141" s="12" t="n"/>
+      <c r="E141" s="14" t="inlineStr">
         <is>
           <t>UDINT</t>
         </is>
       </c>
-      <c r="F131" s="14" t="inlineStr">
+      <c r="F141" s="14" t="inlineStr">
         <is>
           <t>OutputCounter</t>
         </is>
       </c>
-      <c r="G131" s="14" t="inlineStr">
+      <c r="G141" s="14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H131" s="1" t="n"/>
-      <c r="I131" s="1" t="n"/>
-      <c r="L131" s="15" t="inlineStr">
-        <is>
-          <t>rw</t>
-        </is>
-      </c>
-      <c r="M131" s="15" t="inlineStr">
+      <c r="H141" s="1" t="n"/>
+      <c r="I141" s="1" t="n"/>
+      <c r="L141" s="15" t="inlineStr">
+        <is>
+          <t>rw</t>
+        </is>
+      </c>
+      <c r="M141" s="15" t="inlineStr">
         <is>
           <t>rx</t>
         </is>
       </c>
-      <c r="P131" s="1" t="n"/>
-    </row>
-    <row r="132">
-      <c r="B132" s="9" t="inlineStr">
+      <c r="P141" s="1" t="n"/>
+    </row>
+    <row r="142">
+      <c r="B142" s="9" t="inlineStr">
         <is>
           <t>//0x8nnx</t>
         </is>
       </c>
-      <c r="C132" s="9" t="inlineStr">
+      <c r="C142" s="9" t="inlineStr">
         <is>
           <t>Configuration Data of the Module (0x8000 - 0x8FFF)</t>
         </is>
       </c>
-      <c r="D132" s="9" t="n"/>
-      <c r="E132" s="9" t="n"/>
-      <c r="F132" s="9" t="n"/>
-      <c r="G132" s="9" t="n"/>
-      <c r="H132" s="9" t="n"/>
-      <c r="I132" s="9" t="n"/>
-      <c r="J132" s="9" t="n"/>
-      <c r="K132" s="9" t="n"/>
-      <c r="L132" s="9" t="n"/>
-      <c r="M132" s="9" t="n"/>
-      <c r="N132" s="9" t="n"/>
-      <c r="O132" s="9" t="n"/>
-      <c r="P132" s="9" t="n"/>
-    </row>
-    <row r="133">
-      <c r="D133" s="12" t="n"/>
-      <c r="E133" s="1" t="n"/>
-      <c r="F133" s="1" t="n"/>
-      <c r="G133" s="1" t="n"/>
-      <c r="H133" s="1" t="n"/>
-      <c r="I133" s="1" t="n"/>
-      <c r="P133" s="1" t="n"/>
-    </row>
-    <row r="134">
-      <c r="B134" s="9" t="inlineStr">
+      <c r="D142" s="9" t="n"/>
+      <c r="E142" s="9" t="n"/>
+      <c r="F142" s="9" t="n"/>
+      <c r="G142" s="9" t="n"/>
+      <c r="H142" s="9" t="n"/>
+      <c r="I142" s="9" t="n"/>
+      <c r="J142" s="9" t="n"/>
+      <c r="K142" s="9" t="n"/>
+      <c r="L142" s="9" t="n"/>
+      <c r="M142" s="9" t="n"/>
+      <c r="N142" s="9" t="n"/>
+      <c r="O142" s="9" t="n"/>
+      <c r="P142" s="9" t="n"/>
+    </row>
+    <row r="143">
+      <c r="D143" s="12" t="n"/>
+      <c r="E143" s="1" t="n"/>
+      <c r="F143" s="1" t="n"/>
+      <c r="G143" s="1" t="n"/>
+      <c r="H143" s="1" t="n"/>
+      <c r="I143" s="1" t="n"/>
+      <c r="P143" s="1" t="n"/>
+    </row>
+    <row r="144">
+      <c r="B144" s="9" t="inlineStr">
         <is>
           <t>//0x9nnx</t>
         </is>
       </c>
-      <c r="C134" s="9" t="inlineStr">
+      <c r="C144" s="9" t="inlineStr">
         <is>
           <t>Information Data of the Module (0x9000 - 0x9FFF)</t>
         </is>
       </c>
-      <c r="D134" s="9" t="n"/>
-      <c r="E134" s="9" t="n"/>
-      <c r="F134" s="9" t="n"/>
-      <c r="G134" s="9" t="n"/>
-      <c r="H134" s="9" t="n"/>
-      <c r="I134" s="9" t="n"/>
-      <c r="J134" s="9" t="n"/>
-      <c r="K134" s="9" t="n"/>
-      <c r="L134" s="9" t="n"/>
-      <c r="M134" s="9" t="n"/>
-      <c r="N134" s="9" t="n"/>
-      <c r="O134" s="9" t="n"/>
-      <c r="P134" s="9" t="n"/>
-    </row>
-    <row r="135">
-      <c r="D135" s="12" t="n"/>
-      <c r="E135" s="1" t="n"/>
-      <c r="F135" s="1" t="n"/>
-      <c r="G135" s="1" t="n"/>
-      <c r="H135" s="1" t="n"/>
-      <c r="I135" s="1" t="n"/>
-      <c r="P135" s="1" t="n"/>
-    </row>
-    <row r="136">
-      <c r="B136" s="9" t="inlineStr">
+      <c r="D144" s="9" t="n"/>
+      <c r="E144" s="9" t="n"/>
+      <c r="F144" s="9" t="n"/>
+      <c r="G144" s="9" t="n"/>
+      <c r="H144" s="9" t="n"/>
+      <c r="I144" s="9" t="n"/>
+      <c r="J144" s="9" t="n"/>
+      <c r="K144" s="9" t="n"/>
+      <c r="L144" s="9" t="n"/>
+      <c r="M144" s="9" t="n"/>
+      <c r="N144" s="9" t="n"/>
+      <c r="O144" s="9" t="n"/>
+      <c r="P144" s="9" t="n"/>
+    </row>
+    <row r="145">
+      <c r="D145" s="12" t="n"/>
+      <c r="E145" s="1" t="n"/>
+      <c r="F145" s="1" t="n"/>
+      <c r="G145" s="1" t="n"/>
+      <c r="H145" s="1" t="n"/>
+      <c r="I145" s="1" t="n"/>
+      <c r="P145" s="1" t="n"/>
+    </row>
+    <row r="146">
+      <c r="B146" s="9" t="inlineStr">
         <is>
           <t>//0xAnnx</t>
         </is>
       </c>
-      <c r="C136" s="9" t="inlineStr">
+      <c r="C146" s="9" t="inlineStr">
         <is>
           <t>Diagnosis Data of the Module (0xA000 - 0xAFFF)</t>
         </is>
       </c>
-      <c r="D136" s="9" t="n"/>
-      <c r="E136" s="9" t="n"/>
-      <c r="F136" s="9" t="n"/>
-      <c r="G136" s="9" t="n"/>
-      <c r="H136" s="9" t="n"/>
-      <c r="I136" s="9" t="n"/>
-      <c r="J136" s="9" t="n"/>
-      <c r="K136" s="9" t="n"/>
-      <c r="L136" s="9" t="n"/>
-      <c r="M136" s="9" t="n"/>
-      <c r="N136" s="9" t="n"/>
-      <c r="O136" s="9" t="n"/>
-      <c r="P136" s="9" t="n"/>
-    </row>
-    <row r="137"/>
-    <row r="138">
-      <c r="B138" s="16" t="inlineStr">
+      <c r="D146" s="9" t="n"/>
+      <c r="E146" s="9" t="n"/>
+      <c r="F146" s="9" t="n"/>
+      <c r="G146" s="9" t="n"/>
+      <c r="H146" s="9" t="n"/>
+      <c r="I146" s="9" t="n"/>
+      <c r="J146" s="9" t="n"/>
+      <c r="K146" s="9" t="n"/>
+      <c r="L146" s="9" t="n"/>
+      <c r="M146" s="9" t="n"/>
+      <c r="N146" s="9" t="n"/>
+      <c r="O146" s="9" t="n"/>
+      <c r="P146" s="9" t="n"/>
+    </row>
+    <row r="147"/>
+    <row r="148">
+      <c r="B148" s="16" t="inlineStr">
         <is>
           <t>//0xFxxx</t>
         </is>
       </c>
-      <c r="C138" s="16" t="inlineStr">
+      <c r="C148" s="16" t="inlineStr">
         <is>
           <t>Device Objects (0xF000 - 0xFFFF)</t>
         </is>
       </c>
-      <c r="D138" s="16" t="n"/>
-      <c r="E138" s="16" t="n"/>
-      <c r="F138" s="16" t="n"/>
-      <c r="G138" s="16" t="n"/>
-      <c r="H138" s="16" t="n"/>
-      <c r="I138" s="16" t="n"/>
-      <c r="J138" s="16" t="n"/>
-      <c r="K138" s="16" t="n"/>
-      <c r="L138" s="16" t="n"/>
-      <c r="M138" s="16" t="n"/>
-      <c r="N138" s="16" t="n"/>
-      <c r="O138" s="17" t="n"/>
-      <c r="P138" s="17" t="n"/>
-    </row>
-    <row r="139">
-      <c r="B139" t="inlineStr">
+      <c r="D148" s="16" t="n"/>
+      <c r="E148" s="16" t="n"/>
+      <c r="F148" s="16" t="n"/>
+      <c r="G148" s="16" t="n"/>
+      <c r="H148" s="16" t="n"/>
+      <c r="I148" s="16" t="n"/>
+      <c r="J148" s="16" t="n"/>
+      <c r="K148" s="16" t="n"/>
+      <c r="L148" s="16" t="n"/>
+      <c r="M148" s="16" t="n"/>
+      <c r="N148" s="16" t="n"/>
+      <c r="O148" s="17" t="n"/>
+      <c r="P148" s="17" t="n"/>
+    </row>
+    <row r="149">
+      <c r="B149" t="inlineStr">
         <is>
           <t>0xF000</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr">
+      <c r="C149" t="inlineStr">
         <is>
           <t>RECORD</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr">
+      <c r="F149" t="inlineStr">
         <is>
           <t>Modular Device Profile</t>
         </is>
       </c>
-      <c r="J139" t="inlineStr">
+      <c r="J149" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="D140" t="n">
+    <row r="150">
+      <c r="D150" t="n">
         <v>1</v>
       </c>
-      <c r="E140" t="inlineStr">
+      <c r="E150" t="inlineStr">
         <is>
           <t>UINT16</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr">
+      <c r="F150" t="inlineStr">
         <is>
           <t xml:space="preserve">Index distance </t>
         </is>
       </c>
-      <c r="G140" t="inlineStr">
+      <c r="G150" t="inlineStr">
         <is>
           <t>0x10</t>
         </is>
       </c>
-      <c r="J140" t="inlineStr">
+      <c r="J150" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="L140" t="inlineStr">
+      <c r="L150" t="inlineStr">
         <is>
           <t>ro</t>
         </is>
       </c>
-      <c r="N140" s="18" t="n"/>
-    </row>
-    <row r="141">
-      <c r="D141" t="n">
+      <c r="N150" s="18" t="n"/>
+    </row>
+    <row r="151">
+      <c r="D151" t="n">
         <v>2</v>
       </c>
-      <c r="E141" t="inlineStr">
+      <c r="E151" t="inlineStr">
         <is>
           <t>UINT16</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr">
+      <c r="F151" t="inlineStr">
         <is>
           <t xml:space="preserve">Maximum number of modules </t>
         </is>
       </c>
-      <c r="J141" t="inlineStr">
+      <c r="J151" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="L141" t="inlineStr">
+      <c r="L151" t="inlineStr">
         <is>
           <t>ro</t>
         </is>
